--- a/Output/Daily Scan_19 Jul 2026.xlsx
+++ b/Output/Daily Scan_19 Jul 2026.xlsx
@@ -19794,7 +19794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19862,272 +19862,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+          <t>No scanner alerts detected for this interval</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APFC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>JIOFIN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHARATFORG</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASONACOMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EXIDEIND</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATECHM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
